--- a/dataset_t6_grouped/results2/G3/G3_T2485_W0065F0001T0006Z000C1N59_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T2485_W0065F0001T0006Z000C1N59_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>51.964879397049</v>
+        <v>8.444292902020463</v>
       </c>
       <c r="D2" t="n">
-        <v>38.09937663532043</v>
+        <v>6.191148703239569</v>
       </c>
       <c r="E2" t="n">
-        <v>20.59136441396197</v>
+        <v>3.34609671726882</v>
       </c>
       <c r="F2" t="n">
-        <v>12.38762289718061</v>
+        <v>2.01298872079185</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>14.54106050980635</v>
+        <v>2.362922332843532</v>
       </c>
       <c r="D3" t="n">
-        <v>13.9450745791126</v>
+        <v>2.266074619105798</v>
       </c>
       <c r="E3" t="n">
-        <v>20.59136441396197</v>
+        <v>3.34609671726882</v>
       </c>
       <c r="F3" t="n">
-        <v>12.38762289718061</v>
+        <v>2.01298872079185</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>79.3933293394673</v>
+        <v>12.90141601766344</v>
       </c>
       <c r="D4" t="n">
-        <v>32.90900480100628</v>
+        <v>5.34771328016352</v>
       </c>
       <c r="E4" t="n">
-        <v>20.59136441396197</v>
+        <v>3.34609671726882</v>
       </c>
       <c r="F4" t="n">
-        <v>12.38762289718061</v>
+        <v>2.01298872079185</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>47.84878971155864</v>
+        <v>7.77542832812828</v>
       </c>
       <c r="D5" t="n">
-        <v>48.65575925608081</v>
+        <v>7.906560879113131</v>
       </c>
       <c r="E5" t="n">
-        <v>20.59136441396197</v>
+        <v>3.34609671726882</v>
       </c>
       <c r="F5" t="n">
-        <v>12.38762289718061</v>
+        <v>2.01298872079185</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>48.46144995436485</v>
+        <v>7.874985617584289</v>
       </c>
       <c r="D6" t="n">
-        <v>20.47420961444762</v>
+        <v>3.327059062347738</v>
       </c>
       <c r="E6" t="n">
-        <v>20.59136441396197</v>
+        <v>3.34609671726882</v>
       </c>
       <c r="F6" t="n">
-        <v>12.38762289718061</v>
+        <v>2.01298872079185</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
